--- a/GITHUBREPO.xlsx
+++ b/GITHUBREPO.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20632" windowHeight="6963"/>
+    <workbookView windowWidth="20632" windowHeight="7683"/>
   </bookViews>
   <sheets>
     <sheet name="GitHub_DevanshBajpai" sheetId="1" r:id="rId1"/>
@@ -27,12 +27,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
   <si>
     <t xml:space="preserve">Module Name:- </t>
   </si>
   <si>
     <t>GitHub Repositories</t>
+  </si>
+  <si>
+    <t>https://github.com/DevanshBajpai09/ExcelSheetofTestingRepo</t>
   </si>
   <si>
     <t>Submitted By:-</t>
@@ -355,20 +358,12 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>Selenium-Case-Study-1</t>
     </r>
     <r>
       <rPr>
         <i/>
         <sz val="11"/>
-        <color theme="1"/>
         <rFont val="Calibri"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -402,6 +397,30 @@
   </si>
   <si>
     <t>https://github.com/DevanshBajpai09/POSTMAN---CaseStudy</t>
+  </si>
+  <si>
+    <t>RestAssuredTesting , RestAssured-CaseStudy</t>
+  </si>
+  <si>
+    <t>https://github.com/DevanshBajpai09/RestAssuredTesting</t>
+  </si>
+  <si>
+    <t>BDDTestingPostRequestCaseStudy</t>
+  </si>
+  <si>
+    <t>https://github.com/DevanshBajpai09/BDDTestingPostRequestCaseStudy</t>
+  </si>
+  <si>
+    <t>BDDTestingGetRequestCaseStudy</t>
+  </si>
+  <si>
+    <t>https://github.com/DevanshBajpai09/BDDTestingGetRequestCaseStudy</t>
+  </si>
+  <si>
+    <t>ExcelSheetAPITestingCaseStudy</t>
+  </si>
+  <si>
+    <t>https://github.com/DevanshBajpai09/ExcelSheetAPITestingCaseStudy</t>
   </si>
 </sst>
 </file>
@@ -415,12 +434,31 @@
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="180" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -561,22 +599,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -592,6 +622,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -776,7 +812,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -834,6 +870,30 @@
         <color auto="1"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -954,137 +1014,137 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1092,6 +1152,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
@@ -1121,20 +1184,80 @@
     <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1669,12 +1792,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O59"/>
+  <dimension ref="A1:AT62"/>
   <sheetFormatPr defaultColWidth="8.79439252336449" defaultRowHeight="13.95"/>
   <cols>
     <col min="1" max="1" width="18.9719626168224" customWidth="1"/>
     <col min="2" max="2" width="18.0747663551402" customWidth="1"/>
-    <col min="3" max="3" width="52.214953271028" customWidth="1"/>
+    <col min="3" max="3" width="56.7476635514019" customWidth="1"/>
     <col min="4" max="4" width="22.392523364486" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1685,1413 +1808,1580 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2"/>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D1" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2"/>
-      <c r="G1" s="3"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="4">
-        <v>50</v>
+        <v>5</v>
+      </c>
+      <c r="B2" s="5">
+        <v>54</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2"/>
-      <c r="G2" s="3"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="3"/>
+      <c r="G3" s="4"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="3"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:7">
-      <c r="A5" s="7" t="s">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:46">
+      <c r="A5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="8"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="10"/>
+      <c r="P5" s="34"/>
+      <c r="Q5" s="34"/>
+      <c r="R5" s="34"/>
+      <c r="S5" s="34"/>
+      <c r="T5" s="34"/>
+      <c r="U5" s="34"/>
+      <c r="V5" s="34"/>
+      <c r="W5" s="34"/>
+      <c r="X5" s="34"/>
+      <c r="Y5" s="34"/>
+      <c r="Z5" s="34"/>
+      <c r="AA5" s="34"/>
+      <c r="AB5" s="34"/>
+      <c r="AC5" s="34"/>
+      <c r="AD5" s="34"/>
+      <c r="AE5" s="34"/>
+      <c r="AF5" s="34"/>
+      <c r="AG5" s="34"/>
+      <c r="AH5" s="34"/>
+      <c r="AI5" s="34"/>
+      <c r="AJ5" s="34"/>
+      <c r="AK5" s="34"/>
+      <c r="AL5" s="34"/>
+      <c r="AM5" s="34"/>
+      <c r="AN5" s="34"/>
+      <c r="AO5" s="34"/>
+      <c r="AP5" s="34"/>
+      <c r="AQ5" s="34"/>
+      <c r="AR5" s="34"/>
+      <c r="AS5" s="34"/>
+      <c r="AT5" s="34"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="11">
+        <v>1</v>
+      </c>
+      <c r="B6" s="12">
+        <v>46169</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="11">
+        <v>2</v>
+      </c>
+      <c r="B7" s="12">
+        <v>46169</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="18"/>
+      <c r="M7" s="18"/>
+      <c r="N7" s="18"/>
+      <c r="O7" s="18"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="11">
+        <v>3</v>
+      </c>
+      <c r="B8" s="12">
+        <v>46169</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+      <c r="N8" s="18"/>
+      <c r="O8" s="18"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="11">
+        <v>4</v>
+      </c>
+      <c r="B9" s="12">
+        <v>46169</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="18"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="11">
+        <v>5</v>
+      </c>
+      <c r="B10" s="12">
+        <v>46169</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="18"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="11">
+        <v>6</v>
+      </c>
+      <c r="B11" s="12">
+        <v>46169</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="18"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="11">
+        <v>7</v>
+      </c>
+      <c r="B12" s="12">
+        <v>46169</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="18"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18"/>
+      <c r="O12" s="18"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="11">
         <v>8</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B13" s="12">
+        <v>46172</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="18"/>
+      <c r="M13" s="18"/>
+      <c r="N13" s="18"/>
+      <c r="O13" s="18"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="11">
         <v>9</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="B14" s="12">
+        <v>46174</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="35"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="18"/>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="11">
         <v>10</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="B15" s="12">
+        <v>46174</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="35"/>
+      <c r="L15" s="18"/>
+      <c r="M15" s="18"/>
+      <c r="N15" s="18"/>
+      <c r="O15" s="18"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="11">
         <v>11</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="9"/>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" s="10">
-        <v>1</v>
-      </c>
-      <c r="B6" s="11">
-        <v>46200</v>
-      </c>
-      <c r="C6" s="10" t="s">
+      <c r="B16" s="12">
+        <v>46174</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="35"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="18"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="18"/>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" s="11">
         <v>12</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="B17" s="12">
+        <v>46174</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="35"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="18"/>
+      <c r="N17" s="18"/>
+      <c r="O17" s="18"/>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" s="11">
         <v>13</v>
       </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" s="10">
-        <v>2</v>
-      </c>
-      <c r="B7" s="11">
-        <v>46200</v>
-      </c>
-      <c r="C7" s="10" t="s">
+      <c r="B18" s="12">
+        <v>46174</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18"/>
+      <c r="M18" s="18"/>
+      <c r="N18" s="18"/>
+      <c r="O18" s="18"/>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" s="11">
         <v>14</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="B19" s="12">
+        <v>46175</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="18"/>
+      <c r="M19" s="18"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="18"/>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" s="11">
         <v>15</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" s="10">
-        <v>3</v>
-      </c>
-      <c r="B8" s="11">
-        <v>46200</v>
-      </c>
-      <c r="C8" s="10" t="s">
+      <c r="B20" s="12">
+        <v>46175</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="18"/>
+      <c r="L20" s="18"/>
+      <c r="M20" s="18"/>
+      <c r="N20" s="18"/>
+      <c r="O20" s="18"/>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="A21" s="11">
         <v>16</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="B21" s="12">
+        <v>46176</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
+      <c r="M21" s="18"/>
+      <c r="N21" s="18"/>
+      <c r="O21" s="18"/>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" s="11">
         <v>17</v>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" s="10">
-        <v>4</v>
-      </c>
-      <c r="B9" s="11">
-        <v>46200</v>
-      </c>
-      <c r="C9" s="10" t="s">
+      <c r="B22" s="12">
+        <v>46176</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
+      <c r="M22" s="18"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="18"/>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" s="11">
         <v>18</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="B23" s="12">
+        <v>46177</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="18"/>
+      <c r="N23" s="18"/>
+      <c r="O23" s="18"/>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" s="11">
         <v>19</v>
       </c>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10" s="10">
-        <v>5</v>
-      </c>
-      <c r="B10" s="11">
-        <v>46200</v>
-      </c>
-      <c r="C10" s="10" t="s">
+      <c r="B24" s="12">
+        <v>46177</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="18"/>
+      <c r="L24" s="18"/>
+      <c r="M24" s="18"/>
+      <c r="N24" s="18"/>
+      <c r="O24" s="18"/>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" s="11">
         <v>20</v>
       </c>
-      <c r="D10" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="A11" s="10">
-        <v>6</v>
-      </c>
-      <c r="B11" s="11">
-        <v>46200</v>
-      </c>
-      <c r="C11" s="10" t="s">
+      <c r="B25" s="12">
+        <v>46178</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="18"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="18"/>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" s="11">
         <v>22</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="B26" s="12">
+        <v>46178</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
+      <c r="M26" s="18"/>
+      <c r="N26" s="18"/>
+      <c r="O26" s="18"/>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" s="11">
         <v>23</v>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-    </row>
-    <row r="12" spans="1:15">
-      <c r="A12" s="10">
-        <v>7</v>
-      </c>
-      <c r="B12" s="11">
-        <v>46200</v>
-      </c>
-      <c r="C12" s="10" t="s">
+      <c r="B27" s="12">
+        <v>46178</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="18"/>
+      <c r="M27" s="18"/>
+      <c r="N27" s="18"/>
+      <c r="O27" s="18"/>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" s="11">
         <v>24</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="B28" s="12">
+        <v>46178</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="18"/>
+      <c r="M28" s="18"/>
+      <c r="N28" s="18"/>
+      <c r="O28" s="18"/>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" s="11">
         <v>25</v>
       </c>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="A13" s="10">
-        <v>8</v>
-      </c>
-      <c r="B13" s="11">
-        <v>46203</v>
-      </c>
-      <c r="C13" s="10" t="s">
+      <c r="B29" s="12">
+        <v>46181</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
+      <c r="J29" s="18"/>
+      <c r="K29" s="18"/>
+      <c r="L29" s="18"/>
+      <c r="M29" s="18"/>
+      <c r="N29" s="18"/>
+      <c r="O29" s="18"/>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30" s="11">
         <v>26</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="B30" s="12">
+        <v>46181</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="18"/>
+      <c r="K30" s="18"/>
+      <c r="L30" s="18"/>
+      <c r="M30" s="18"/>
+      <c r="N30" s="18"/>
+      <c r="O30" s="18"/>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" s="11">
         <v>27</v>
       </c>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-    </row>
-    <row r="14" spans="1:15">
-      <c r="A14" s="10">
-        <v>9</v>
-      </c>
-      <c r="B14" s="11">
-        <v>46204</v>
-      </c>
-      <c r="C14" s="10" t="s">
+      <c r="B31" s="12">
+        <v>46182</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
+      <c r="J31" s="18"/>
+      <c r="K31" s="18"/>
+      <c r="L31" s="18"/>
+      <c r="M31" s="18"/>
+      <c r="N31" s="18"/>
+      <c r="O31" s="18"/>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="A32" s="11">
         <v>28</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="B32" s="12">
+        <v>46182</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
+      <c r="M32" s="18"/>
+      <c r="N32" s="18"/>
+      <c r="O32" s="18"/>
+    </row>
+    <row r="33" spans="1:15">
+      <c r="A33" s="11">
         <v>29</v>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
-    </row>
-    <row r="15" spans="1:15">
-      <c r="A15" s="10">
-        <v>10</v>
-      </c>
-      <c r="B15" s="11">
-        <v>46204</v>
-      </c>
-      <c r="C15" s="10" t="s">
+      <c r="B33" s="12">
+        <v>46183</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="18"/>
+      <c r="K33" s="18"/>
+      <c r="L33" s="18"/>
+      <c r="M33" s="18"/>
+      <c r="N33" s="18"/>
+      <c r="O33" s="18"/>
+    </row>
+    <row r="34" spans="1:15">
+      <c r="A34" s="11">
         <v>30</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="B34" s="12">
+        <v>46183</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="18"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="18"/>
+      <c r="M34" s="18"/>
+      <c r="N34" s="18"/>
+      <c r="O34" s="18"/>
+    </row>
+    <row r="35" spans="1:15">
+      <c r="A35" s="11">
         <v>31</v>
       </c>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
-    </row>
-    <row r="16" spans="1:15">
-      <c r="A16" s="10">
-        <v>11</v>
-      </c>
-      <c r="B16" s="11">
-        <v>46204</v>
-      </c>
-      <c r="C16" s="10" t="s">
+      <c r="B35" s="12">
+        <v>46184</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="18"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18"/>
+      <c r="M35" s="18"/>
+      <c r="N35" s="18"/>
+      <c r="O35" s="18"/>
+    </row>
+    <row r="36" spans="1:15">
+      <c r="A36" s="11">
         <v>32</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="B36" s="12">
+        <v>46184</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="18"/>
+      <c r="K36" s="18"/>
+      <c r="L36" s="18"/>
+      <c r="M36" s="18"/>
+      <c r="N36" s="18"/>
+      <c r="O36" s="18"/>
+    </row>
+    <row r="37" spans="1:15">
+      <c r="A37" s="11">
         <v>33</v>
       </c>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
-      <c r="O16" s="10"/>
-    </row>
-    <row r="17" spans="1:15">
-      <c r="A17" s="10">
-        <v>12</v>
-      </c>
-      <c r="B17" s="11">
-        <v>46204</v>
-      </c>
-      <c r="C17" s="10" t="s">
+      <c r="B37" s="12">
+        <v>46185</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E37" s="15"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
+      <c r="J37" s="18"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="18"/>
+      <c r="M37" s="18"/>
+      <c r="N37" s="18"/>
+      <c r="O37" s="18"/>
+    </row>
+    <row r="38" spans="1:15">
+      <c r="A38" s="11">
         <v>34</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="B38" s="12">
+        <v>46185</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+      <c r="M38" s="18"/>
+      <c r="N38" s="18"/>
+      <c r="O38" s="18"/>
+    </row>
+    <row r="39" spans="1:15">
+      <c r="A39" s="11">
         <v>35</v>
       </c>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
-    </row>
-    <row r="18" spans="1:15">
-      <c r="A18" s="10">
-        <v>13</v>
-      </c>
-      <c r="B18" s="11">
-        <v>46204</v>
-      </c>
-      <c r="C18" s="10" t="s">
+      <c r="B39" s="12">
+        <v>46170</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="E39" s="15"/>
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="18"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+      <c r="M39" s="18"/>
+      <c r="N39" s="18"/>
+      <c r="O39" s="18"/>
+    </row>
+    <row r="40" ht="38" customHeight="1" spans="1:15">
+      <c r="A40" s="11">
         <v>36</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="B40" s="12">
+        <v>46171</v>
+      </c>
+      <c r="C40" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+      <c r="I40" s="15"/>
+      <c r="J40" s="15"/>
+      <c r="K40" s="15"/>
+      <c r="L40" s="15"/>
+      <c r="M40" s="15"/>
+      <c r="N40" s="15"/>
+      <c r="O40" s="15"/>
+    </row>
+    <row r="41" spans="1:15">
+      <c r="A41" s="11">
         <v>37</v>
       </c>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
-      <c r="O18" s="10"/>
-    </row>
-    <row r="19" spans="1:15">
-      <c r="A19" s="10">
-        <v>14</v>
-      </c>
-      <c r="B19" s="11">
-        <v>46205</v>
-      </c>
-      <c r="C19" s="10" t="s">
+      <c r="B41" s="12">
+        <v>46186</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D41" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="21"/>
+      <c r="I41" s="21"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+      <c r="M41" s="18"/>
+      <c r="N41" s="18"/>
+      <c r="O41" s="18"/>
+    </row>
+    <row r="42" spans="1:15">
+      <c r="A42" s="11">
         <v>38</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="B42" s="12">
+        <v>46186</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="D42" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="15"/>
+      <c r="I42" s="15"/>
+      <c r="J42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
+      <c r="M42" s="18"/>
+      <c r="N42" s="18"/>
+      <c r="O42" s="18"/>
+    </row>
+    <row r="43" spans="1:15">
+      <c r="A43" s="11">
         <v>39</v>
       </c>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
-      <c r="O19" s="10"/>
-    </row>
-    <row r="20" spans="1:15">
-      <c r="A20" s="10">
-        <v>15</v>
-      </c>
-      <c r="B20" s="11">
-        <v>46205</v>
-      </c>
-      <c r="C20" s="10" t="s">
+      <c r="B43" s="12">
+        <v>46186</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="18"/>
+      <c r="J43" s="18"/>
+      <c r="K43" s="18"/>
+      <c r="L43" s="18"/>
+      <c r="M43" s="18"/>
+      <c r="N43" s="18"/>
+      <c r="O43" s="18"/>
+    </row>
+    <row r="44" spans="1:15">
+      <c r="A44" s="11">
         <v>40</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="B44" s="12">
+        <v>46187</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="E44" s="15"/>
+      <c r="F44" s="15"/>
+      <c r="G44" s="15"/>
+      <c r="H44" s="15"/>
+      <c r="I44" s="15"/>
+      <c r="J44" s="18"/>
+      <c r="K44" s="18"/>
+      <c r="L44" s="18"/>
+      <c r="M44" s="18"/>
+      <c r="N44" s="18"/>
+      <c r="O44" s="18"/>
+    </row>
+    <row r="45" spans="1:15">
+      <c r="A45" s="11">
         <v>41</v>
       </c>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10"/>
-      <c r="O20" s="10"/>
-    </row>
-    <row r="21" spans="1:15">
-      <c r="A21" s="10">
-        <v>16</v>
-      </c>
-      <c r="B21" s="11">
-        <v>46206</v>
-      </c>
-      <c r="C21" s="10" t="s">
+      <c r="B45" s="12">
+        <v>46187</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="E45" s="15"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="15"/>
+      <c r="H45" s="15"/>
+      <c r="I45" s="15"/>
+      <c r="J45" s="18"/>
+      <c r="K45" s="18"/>
+      <c r="L45" s="18"/>
+      <c r="M45" s="18"/>
+      <c r="N45" s="18"/>
+      <c r="O45" s="18"/>
+    </row>
+    <row r="46" spans="1:15">
+      <c r="A46" s="11">
         <v>42</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="B46" s="12">
+        <v>46187</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="E46" s="15"/>
+      <c r="F46" s="15"/>
+      <c r="G46" s="15"/>
+      <c r="H46" s="15"/>
+      <c r="I46" s="15"/>
+      <c r="J46" s="18"/>
+      <c r="K46" s="18"/>
+      <c r="L46" s="18"/>
+      <c r="M46" s="18"/>
+      <c r="N46" s="18"/>
+      <c r="O46" s="18"/>
+    </row>
+    <row r="47" spans="1:15">
+      <c r="A47" s="11">
         <v>43</v>
       </c>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
-      <c r="O21" s="10"/>
-    </row>
-    <row r="22" spans="1:15">
-      <c r="A22" s="10">
-        <v>17</v>
-      </c>
-      <c r="B22" s="11">
-        <v>46206</v>
-      </c>
-      <c r="C22" s="10" t="s">
+      <c r="B47" s="12">
+        <v>46187</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="E47" s="15"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="15"/>
+      <c r="H47" s="15"/>
+      <c r="I47" s="15"/>
+      <c r="J47" s="18"/>
+      <c r="K47" s="18"/>
+      <c r="L47" s="18"/>
+      <c r="M47" s="18"/>
+      <c r="N47" s="18"/>
+      <c r="O47" s="18"/>
+    </row>
+    <row r="48" spans="1:15">
+      <c r="A48" s="11">
         <v>44</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="B48" s="12">
+        <v>46187</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="E48" s="17"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="35"/>
+      <c r="J48" s="18"/>
+      <c r="K48" s="18"/>
+      <c r="L48" s="18"/>
+      <c r="M48" s="18"/>
+      <c r="N48" s="18"/>
+      <c r="O48" s="18"/>
+    </row>
+    <row r="49" spans="1:15">
+      <c r="A49" s="11">
         <v>45</v>
       </c>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="10"/>
-      <c r="O22" s="10"/>
-    </row>
-    <row r="23" spans="1:15">
-      <c r="A23" s="10">
-        <v>18</v>
-      </c>
-      <c r="B23" s="11">
-        <v>46207</v>
-      </c>
-      <c r="C23" s="10" t="s">
+      <c r="B49" s="12">
+        <v>46187</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="D49" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="E49" s="17"/>
+      <c r="F49" s="17"/>
+      <c r="G49" s="17"/>
+      <c r="H49" s="17"/>
+      <c r="I49" s="35"/>
+      <c r="J49" s="18"/>
+      <c r="K49" s="18"/>
+      <c r="L49" s="18"/>
+      <c r="M49" s="18"/>
+      <c r="N49" s="18"/>
+      <c r="O49" s="18"/>
+    </row>
+    <row r="50" spans="1:15">
+      <c r="A50" s="11">
         <v>46</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="B50" s="12">
+        <v>46187</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="E50" s="17"/>
+      <c r="F50" s="17"/>
+      <c r="G50" s="17"/>
+      <c r="H50" s="17"/>
+      <c r="I50" s="35"/>
+      <c r="J50" s="18"/>
+      <c r="K50" s="18"/>
+      <c r="L50" s="18"/>
+      <c r="M50" s="18"/>
+      <c r="N50" s="18"/>
+      <c r="O50" s="18"/>
+    </row>
+    <row r="51" spans="1:15">
+      <c r="A51" s="11">
         <v>47</v>
       </c>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
-      <c r="O23" s="10"/>
-    </row>
-    <row r="24" spans="1:15">
-      <c r="A24" s="10">
-        <v>19</v>
-      </c>
-      <c r="B24" s="11">
-        <v>46207</v>
-      </c>
-      <c r="C24" s="10" t="s">
+      <c r="B51" s="12">
+        <v>46187</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D51" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="E51" s="17"/>
+      <c r="F51" s="17"/>
+      <c r="G51" s="17"/>
+      <c r="H51" s="17"/>
+      <c r="I51" s="35"/>
+      <c r="J51" s="18"/>
+      <c r="K51" s="18"/>
+      <c r="L51" s="18"/>
+      <c r="M51" s="18"/>
+      <c r="N51" s="18"/>
+      <c r="O51" s="18"/>
+    </row>
+    <row r="52" spans="1:15">
+      <c r="A52" s="11">
         <v>48</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="B52" s="12">
+        <v>46187</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="D52" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="E52" s="17"/>
+      <c r="F52" s="17"/>
+      <c r="G52" s="17"/>
+      <c r="H52" s="17"/>
+      <c r="I52" s="35"/>
+      <c r="J52" s="18"/>
+      <c r="K52" s="18"/>
+      <c r="L52" s="18"/>
+      <c r="M52" s="18"/>
+      <c r="N52" s="18"/>
+      <c r="O52" s="18"/>
+    </row>
+    <row r="53" spans="1:15">
+      <c r="A53" s="11">
         <v>49</v>
       </c>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="10"/>
-      <c r="O24" s="10"/>
-    </row>
-    <row r="25" spans="1:15">
-      <c r="A25" s="10">
-        <v>20</v>
-      </c>
-      <c r="B25" s="11">
-        <v>46208</v>
-      </c>
-      <c r="C25" s="10" t="s">
+      <c r="B53" s="12">
+        <v>46187</v>
+      </c>
+      <c r="C53" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="D53" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="E53" s="17"/>
+      <c r="F53" s="17"/>
+      <c r="G53" s="17"/>
+      <c r="H53" s="17"/>
+      <c r="I53" s="35"/>
+      <c r="J53" s="18"/>
+      <c r="K53" s="18"/>
+      <c r="L53" s="18"/>
+      <c r="M53" s="18"/>
+      <c r="N53" s="18"/>
+      <c r="O53" s="18"/>
+    </row>
+    <row r="54" spans="1:15">
+      <c r="A54" s="11">
         <v>50</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="B54" s="12">
+        <v>46187</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="D54" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="E54" s="17"/>
+      <c r="F54" s="17"/>
+      <c r="G54" s="17"/>
+      <c r="H54" s="17"/>
+      <c r="I54" s="35"/>
+      <c r="J54" s="18"/>
+      <c r="K54" s="18"/>
+      <c r="L54" s="18"/>
+      <c r="M54" s="18"/>
+      <c r="N54" s="18"/>
+      <c r="O54" s="18"/>
+    </row>
+    <row r="55" spans="1:15">
+      <c r="A55" s="11">
         <v>51</v>
       </c>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="10"/>
-      <c r="O25" s="10"/>
-    </row>
-    <row r="26" spans="1:15">
-      <c r="A26" s="10">
-        <v>22</v>
-      </c>
-      <c r="B26" s="11">
-        <v>46208</v>
-      </c>
-      <c r="C26" s="10" t="s">
+      <c r="B55" s="12">
+        <v>46187</v>
+      </c>
+      <c r="C55" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D55" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="E55" s="17"/>
+      <c r="F55" s="17"/>
+      <c r="G55" s="17"/>
+      <c r="H55" s="17"/>
+      <c r="I55" s="35"/>
+      <c r="J55" s="18"/>
+      <c r="K55" s="18"/>
+      <c r="L55" s="18"/>
+      <c r="M55" s="18"/>
+      <c r="N55" s="18"/>
+      <c r="O55" s="18"/>
+    </row>
+    <row r="56" spans="1:15">
+      <c r="A56" s="11">
         <v>52</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="B56" s="12">
+        <v>46187</v>
+      </c>
+      <c r="C56" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D56" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="E56" s="15"/>
+      <c r="F56" s="15"/>
+      <c r="G56" s="15"/>
+      <c r="H56" s="15"/>
+      <c r="I56" s="15"/>
+      <c r="J56" s="18"/>
+      <c r="K56" s="18"/>
+      <c r="L56" s="18"/>
+      <c r="M56" s="18"/>
+      <c r="N56" s="18"/>
+      <c r="O56" s="18"/>
+    </row>
+    <row r="57" spans="1:15">
+      <c r="A57" s="11">
         <v>53</v>
       </c>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="10"/>
-      <c r="M26" s="10"/>
-      <c r="N26" s="10"/>
-      <c r="O26" s="10"/>
-    </row>
-    <row r="27" spans="1:15">
-      <c r="A27" s="10">
-        <v>23</v>
-      </c>
-      <c r="B27" s="11">
-        <v>46209</v>
-      </c>
-      <c r="C27" s="10" t="s">
+      <c r="B57" s="12">
+        <v>46190</v>
+      </c>
+      <c r="C57" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="D57" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="E57" s="17"/>
+      <c r="F57" s="17"/>
+      <c r="G57" s="17"/>
+      <c r="H57" s="17"/>
+      <c r="I57" s="35"/>
+      <c r="J57" s="18"/>
+      <c r="K57" s="18"/>
+      <c r="L57" s="18"/>
+      <c r="M57" s="18"/>
+      <c r="N57" s="18"/>
+      <c r="O57" s="18"/>
+    </row>
+    <row r="58" spans="1:15">
+      <c r="A58" s="11">
         <v>54</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="B58" s="12">
+        <v>46191</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D58" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="E58" s="15"/>
+      <c r="F58" s="15"/>
+      <c r="G58" s="15"/>
+      <c r="H58" s="15"/>
+      <c r="I58" s="15"/>
+      <c r="J58" s="18"/>
+      <c r="K58" s="18"/>
+      <c r="L58" s="18"/>
+      <c r="M58" s="18"/>
+      <c r="N58" s="18"/>
+      <c r="O58" s="18"/>
+    </row>
+    <row r="59" spans="1:15">
+      <c r="A59" s="22">
         <v>55</v>
       </c>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10"/>
-      <c r="M27" s="10"/>
-      <c r="N27" s="10"/>
-      <c r="O27" s="10"/>
-    </row>
-    <row r="28" spans="1:15">
-      <c r="A28" s="10">
-        <v>24</v>
-      </c>
-      <c r="B28" s="11">
-        <v>46209</v>
-      </c>
-      <c r="C28" s="10" t="s">
+      <c r="B59" s="23">
+        <v>46192</v>
+      </c>
+      <c r="C59" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="D59" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="E59" s="26"/>
+      <c r="F59" s="26"/>
+      <c r="G59" s="26"/>
+      <c r="H59" s="26"/>
+      <c r="I59" s="26"/>
+      <c r="J59" s="36"/>
+      <c r="K59" s="36"/>
+      <c r="L59" s="36"/>
+      <c r="M59" s="36"/>
+      <c r="N59" s="36"/>
+      <c r="O59" s="36"/>
+    </row>
+    <row r="60" spans="1:15">
+      <c r="A60" s="27">
         <v>56</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="B60" s="28">
+        <v>46192</v>
+      </c>
+      <c r="C60" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="D60" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="E60" s="31"/>
+      <c r="F60" s="31"/>
+      <c r="G60" s="31"/>
+      <c r="H60" s="31"/>
+      <c r="I60" s="31"/>
+      <c r="J60" s="37"/>
+      <c r="K60" s="37"/>
+      <c r="L60" s="37"/>
+      <c r="M60" s="37"/>
+      <c r="N60" s="37"/>
+      <c r="O60" s="37"/>
+    </row>
+    <row r="61" spans="1:15">
+      <c r="A61" s="27">
         <v>57</v>
       </c>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="10"/>
-      <c r="M28" s="10"/>
-      <c r="N28" s="10"/>
-      <c r="O28" s="10"/>
-    </row>
-    <row r="29" spans="1:15">
-      <c r="A29" s="10">
-        <v>25</v>
-      </c>
-      <c r="B29" s="11">
-        <v>46211</v>
-      </c>
-      <c r="C29" s="10" t="s">
+      <c r="B61" s="28">
+        <v>46192</v>
+      </c>
+      <c r="C61" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="D61" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="E61" s="31"/>
+      <c r="F61" s="31"/>
+      <c r="G61" s="31"/>
+      <c r="H61" s="31"/>
+      <c r="I61" s="31"/>
+      <c r="J61" s="37"/>
+      <c r="K61" s="37"/>
+      <c r="L61" s="37"/>
+      <c r="M61" s="37"/>
+      <c r="N61" s="37"/>
+      <c r="O61" s="37"/>
+    </row>
+    <row r="62" spans="1:15">
+      <c r="A62" s="32">
         <v>58</v>
       </c>
-      <c r="D29" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
-      <c r="M29" s="10"/>
-      <c r="N29" s="10"/>
-      <c r="O29" s="10"/>
-    </row>
-    <row r="30" spans="1:15">
-      <c r="A30" s="10">
-        <v>26</v>
-      </c>
-      <c r="B30" s="11">
-        <v>46211</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="10"/>
-      <c r="M30" s="10"/>
-      <c r="N30" s="10"/>
-      <c r="O30" s="10"/>
-    </row>
-    <row r="31" spans="1:15">
-      <c r="A31" s="10">
-        <v>27</v>
-      </c>
-      <c r="B31" s="11">
-        <v>46212</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="10"/>
-      <c r="M31" s="10"/>
-      <c r="N31" s="10"/>
-      <c r="O31" s="10"/>
-    </row>
-    <row r="32" spans="1:15">
-      <c r="A32" s="10">
-        <v>28</v>
-      </c>
-      <c r="B32" s="11">
-        <v>46212</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
-      <c r="L32" s="10"/>
-      <c r="M32" s="10"/>
-      <c r="N32" s="10"/>
-      <c r="O32" s="10"/>
-    </row>
-    <row r="33" spans="1:15">
-      <c r="A33" s="10">
-        <v>29</v>
-      </c>
-      <c r="B33" s="11">
-        <v>46213</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="10"/>
-      <c r="K33" s="10"/>
-      <c r="L33" s="10"/>
-      <c r="M33" s="10"/>
-      <c r="N33" s="10"/>
-      <c r="O33" s="10"/>
-    </row>
-    <row r="34" spans="1:15">
-      <c r="A34" s="10">
-        <v>30</v>
-      </c>
-      <c r="B34" s="11">
-        <v>46213</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="10"/>
-      <c r="L34" s="10"/>
-      <c r="M34" s="10"/>
-      <c r="N34" s="10"/>
-      <c r="O34" s="10"/>
-    </row>
-    <row r="35" spans="1:15">
-      <c r="A35" s="10">
-        <v>31</v>
-      </c>
-      <c r="B35" s="11">
-        <v>46214</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="10"/>
-      <c r="K35" s="10"/>
-      <c r="L35" s="10"/>
-      <c r="M35" s="10"/>
-      <c r="N35" s="10"/>
-      <c r="O35" s="10"/>
-    </row>
-    <row r="36" spans="1:15">
-      <c r="A36" s="10">
-        <v>32</v>
-      </c>
-      <c r="B36" s="11">
-        <v>46214</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10"/>
-      <c r="K36" s="10"/>
-      <c r="L36" s="10"/>
-      <c r="M36" s="10"/>
-      <c r="N36" s="10"/>
-      <c r="O36" s="10"/>
-    </row>
-    <row r="37" spans="1:15">
-      <c r="A37" s="10">
-        <v>33</v>
-      </c>
-      <c r="B37" s="11">
-        <v>46215</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
-      <c r="N37" s="10"/>
-      <c r="O37" s="10"/>
-    </row>
-    <row r="38" spans="1:15">
-      <c r="A38" s="10">
-        <v>34</v>
-      </c>
-      <c r="B38" s="11">
-        <v>46215</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10"/>
-      <c r="M38" s="10"/>
-      <c r="N38" s="10"/>
-      <c r="O38" s="10"/>
-    </row>
-    <row r="39" spans="1:15">
-      <c r="A39" s="10">
-        <v>35</v>
-      </c>
-      <c r="B39" s="11">
-        <v>46201</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="10"/>
-      <c r="K39" s="10"/>
-      <c r="L39" s="10"/>
-      <c r="M39" s="10"/>
-      <c r="N39" s="10"/>
-      <c r="O39" s="10"/>
-    </row>
-    <row r="40" ht="38" customHeight="1" spans="1:15">
-      <c r="A40" s="10">
-        <v>36</v>
-      </c>
-      <c r="B40" s="11">
-        <v>46202</v>
-      </c>
-      <c r="C40" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
-      <c r="K40" s="10"/>
-      <c r="L40" s="10"/>
-      <c r="M40" s="10"/>
-      <c r="N40" s="10"/>
-      <c r="O40" s="10"/>
-    </row>
-    <row r="41" spans="1:15">
-      <c r="A41" s="10">
-        <v>37</v>
-      </c>
-      <c r="B41" s="11">
-        <v>46216</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
-      <c r="J41" s="10"/>
-      <c r="K41" s="10"/>
-      <c r="L41" s="10"/>
-      <c r="M41" s="10"/>
-      <c r="N41" s="10"/>
-      <c r="O41" s="10"/>
-    </row>
-    <row r="42" spans="1:15">
-      <c r="A42" s="10">
-        <v>38</v>
-      </c>
-      <c r="B42" s="11">
-        <v>46216</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="10"/>
-      <c r="J42" s="10"/>
-      <c r="K42" s="10"/>
-      <c r="L42" s="10"/>
-      <c r="M42" s="10"/>
-      <c r="N42" s="10"/>
-      <c r="O42" s="10"/>
-    </row>
-    <row r="43" spans="1:15">
-      <c r="A43" s="10">
-        <v>39</v>
-      </c>
-      <c r="B43" s="11">
-        <v>46216</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="D43" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
-      <c r="K43" s="10"/>
-      <c r="L43" s="10"/>
-      <c r="M43" s="10"/>
-      <c r="N43" s="10"/>
-      <c r="O43" s="10"/>
-    </row>
-    <row r="44" spans="1:15">
-      <c r="A44" s="10">
-        <v>40</v>
-      </c>
-      <c r="B44" s="11">
-        <v>46217</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="D44" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
-      <c r="K44" s="10"/>
-      <c r="L44" s="10"/>
-      <c r="M44" s="10"/>
-      <c r="N44" s="10"/>
-      <c r="O44" s="10"/>
-    </row>
-    <row r="45" spans="1:15">
-      <c r="A45" s="10">
-        <v>41</v>
-      </c>
-      <c r="B45" s="11">
-        <v>46217</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="10"/>
-      <c r="K45" s="10"/>
-      <c r="L45" s="10"/>
-      <c r="M45" s="10"/>
-      <c r="N45" s="10"/>
-      <c r="O45" s="10"/>
-    </row>
-    <row r="46" spans="1:15">
-      <c r="A46" s="10">
-        <v>42</v>
-      </c>
-      <c r="B46" s="11">
-        <v>46217</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D46" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10"/>
-      <c r="L46" s="10"/>
-      <c r="M46" s="10"/>
-      <c r="N46" s="10"/>
-      <c r="O46" s="10"/>
-    </row>
-    <row r="47" spans="1:15">
-      <c r="A47" s="10">
-        <v>43</v>
-      </c>
-      <c r="B47" s="11">
-        <v>46217</v>
-      </c>
-      <c r="C47" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="D47" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
-      <c r="K47" s="10"/>
-      <c r="L47" s="10"/>
-      <c r="M47" s="10"/>
-      <c r="N47" s="10"/>
-      <c r="O47" s="10"/>
-    </row>
-    <row r="48" spans="1:15">
-      <c r="A48" s="10">
-        <v>44</v>
-      </c>
-      <c r="B48" s="11">
-        <v>46217</v>
-      </c>
-      <c r="C48" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="D48" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="10"/>
-      <c r="L48" s="10"/>
-      <c r="M48" s="10"/>
-      <c r="N48" s="10"/>
-      <c r="O48" s="10"/>
-    </row>
-    <row r="49" spans="1:15">
-      <c r="A49" s="10">
-        <v>45</v>
-      </c>
-      <c r="B49" s="11">
-        <v>46217</v>
-      </c>
-      <c r="C49" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="D49" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="10"/>
-      <c r="K49" s="10"/>
-      <c r="L49" s="10"/>
-      <c r="M49" s="10"/>
-      <c r="N49" s="10"/>
-      <c r="O49" s="10"/>
-    </row>
-    <row r="50" spans="1:15">
-      <c r="A50" s="10">
-        <v>46</v>
-      </c>
-      <c r="B50" s="11">
-        <v>46217</v>
-      </c>
-      <c r="C50" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="D50" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="E50" s="10"/>
-      <c r="F50" s="10"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
-      <c r="I50" s="10"/>
-      <c r="J50" s="10"/>
-      <c r="K50" s="10"/>
-      <c r="L50" s="10"/>
-      <c r="M50" s="10"/>
-      <c r="N50" s="10"/>
-      <c r="O50" s="10"/>
-    </row>
-    <row r="51" spans="1:15">
-      <c r="A51" s="10">
-        <v>47</v>
-      </c>
-      <c r="B51" s="11">
-        <v>46217</v>
-      </c>
-      <c r="C51" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D51" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="10"/>
-      <c r="L51" s="10"/>
-      <c r="M51" s="10"/>
-      <c r="N51" s="10"/>
-      <c r="O51" s="10"/>
-    </row>
-    <row r="52" spans="1:15">
-      <c r="A52" s="10">
-        <v>48</v>
-      </c>
-      <c r="B52" s="11">
-        <v>46217</v>
-      </c>
-      <c r="C52" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="D52" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E52" s="10"/>
-      <c r="F52" s="10"/>
-      <c r="G52" s="10"/>
-      <c r="H52" s="10"/>
-      <c r="I52" s="10"/>
-      <c r="J52" s="10"/>
-      <c r="K52" s="10"/>
-      <c r="L52" s="10"/>
-      <c r="M52" s="10"/>
-      <c r="N52" s="10"/>
-      <c r="O52" s="10"/>
-    </row>
-    <row r="53" spans="1:15">
-      <c r="A53" s="10">
-        <v>49</v>
-      </c>
-      <c r="B53" s="11">
-        <v>46217</v>
-      </c>
-      <c r="C53" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="D53" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="10"/>
-      <c r="K53" s="10"/>
-      <c r="L53" s="10"/>
-      <c r="M53" s="10"/>
-      <c r="N53" s="10"/>
-      <c r="O53" s="10"/>
-    </row>
-    <row r="54" spans="1:15">
-      <c r="A54" s="10">
-        <v>50</v>
-      </c>
-      <c r="B54" s="11">
-        <v>46217</v>
-      </c>
-      <c r="C54" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="D54" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="10"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="10"/>
-      <c r="K54" s="10"/>
-      <c r="L54" s="10"/>
-      <c r="M54" s="10"/>
-      <c r="N54" s="10"/>
-      <c r="O54" s="10"/>
-    </row>
-    <row r="55" spans="1:15">
-      <c r="A55" s="10">
-        <v>51</v>
-      </c>
-      <c r="B55" s="11">
-        <v>46217</v>
-      </c>
-      <c r="C55" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="D55" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="E55" s="10"/>
-      <c r="F55" s="10"/>
-      <c r="G55" s="10"/>
-      <c r="H55" s="10"/>
-      <c r="I55" s="10"/>
-      <c r="J55" s="10"/>
-      <c r="K55" s="10"/>
-      <c r="L55" s="10"/>
-      <c r="M55" s="10"/>
-      <c r="N55" s="10"/>
-      <c r="O55" s="10"/>
-    </row>
-    <row r="56" spans="1:15">
-      <c r="A56" s="10">
-        <v>52</v>
-      </c>
-      <c r="B56" s="11">
-        <v>46217</v>
-      </c>
-      <c r="C56" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="D56" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="E56" s="10"/>
-      <c r="F56" s="10"/>
-      <c r="G56" s="10"/>
-      <c r="H56" s="10"/>
-      <c r="I56" s="10"/>
-      <c r="J56" s="10"/>
-      <c r="K56" s="10"/>
-      <c r="L56" s="10"/>
-      <c r="M56" s="10"/>
-      <c r="N56" s="10"/>
-      <c r="O56" s="10"/>
-    </row>
-    <row r="57" spans="1:15">
-      <c r="A57" s="10">
-        <v>53</v>
-      </c>
-      <c r="B57" s="11">
-        <v>46220</v>
-      </c>
-      <c r="C57" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D57" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="E57" s="10"/>
-      <c r="F57" s="10"/>
-      <c r="G57" s="10"/>
-      <c r="H57" s="10"/>
-      <c r="I57" s="10"/>
-      <c r="J57" s="10"/>
-      <c r="K57" s="10"/>
-      <c r="L57" s="10"/>
-      <c r="M57" s="10"/>
-      <c r="N57" s="10"/>
-      <c r="O57" s="10"/>
-    </row>
-    <row r="58" spans="1:15">
-      <c r="A58" s="10">
-        <v>54</v>
-      </c>
-      <c r="B58" s="11">
-        <v>46222</v>
-      </c>
-      <c r="C58" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="E58" s="10"/>
-      <c r="F58" s="10"/>
-      <c r="G58" s="10"/>
-      <c r="H58" s="10"/>
-      <c r="I58" s="10"/>
-      <c r="J58" s="10"/>
-      <c r="K58" s="10"/>
-      <c r="L58" s="10"/>
-      <c r="M58" s="10"/>
-      <c r="N58" s="10"/>
-      <c r="O58" s="10"/>
-    </row>
-    <row r="59" spans="1:15">
-      <c r="A59" s="16"/>
-      <c r="B59" s="16"/>
-      <c r="C59" s="16"/>
-      <c r="D59" s="16"/>
-      <c r="E59" s="16"/>
-      <c r="F59" s="16"/>
-      <c r="G59" s="16"/>
-      <c r="H59" s="16"/>
-      <c r="I59" s="16"/>
-      <c r="J59" s="16"/>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="16"/>
-      <c r="O59" s="16"/>
+      <c r="B62" s="33">
+        <v>46193</v>
+      </c>
+      <c r="C62" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="D62" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="E62" s="32"/>
+      <c r="F62" s="32"/>
+      <c r="G62" s="32"/>
+      <c r="H62" s="32"/>
+      <c r="I62" s="32"/>
+      <c r="J62" s="32"/>
+      <c r="K62" s="32"/>
+      <c r="L62" s="32"/>
+      <c r="M62" s="32"/>
+      <c r="N62" s="32"/>
+      <c r="O62" s="32"/>
     </row>
   </sheetData>
+  <mergeCells count="49">
+    <mergeCell ref="D6:I6"/>
+    <mergeCell ref="D7:I7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="D12:K12"/>
+    <mergeCell ref="D13:K13"/>
+    <mergeCell ref="D14:K14"/>
+    <mergeCell ref="D15:K15"/>
+    <mergeCell ref="D16:K16"/>
+    <mergeCell ref="D17:K17"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="D22:I22"/>
+    <mergeCell ref="D23:I23"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="D26:I26"/>
+    <mergeCell ref="D27:I27"/>
+    <mergeCell ref="D29:I29"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D34:I34"/>
+    <mergeCell ref="D35:I35"/>
+    <mergeCell ref="D36:I36"/>
+    <mergeCell ref="D37:I37"/>
+    <mergeCell ref="D38:I38"/>
+    <mergeCell ref="D39:I39"/>
+    <mergeCell ref="D40:O40"/>
+    <mergeCell ref="D41:I41"/>
+    <mergeCell ref="D42:I42"/>
+    <mergeCell ref="D44:I44"/>
+    <mergeCell ref="D45:I45"/>
+    <mergeCell ref="D46:I46"/>
+    <mergeCell ref="D47:I47"/>
+    <mergeCell ref="D48:I48"/>
+    <mergeCell ref="D49:I49"/>
+    <mergeCell ref="D50:I50"/>
+    <mergeCell ref="D51:I51"/>
+    <mergeCell ref="D52:I52"/>
+    <mergeCell ref="D53:I53"/>
+    <mergeCell ref="D54:I54"/>
+    <mergeCell ref="D55:I55"/>
+    <mergeCell ref="D56:I56"/>
+    <mergeCell ref="D57:I57"/>
+    <mergeCell ref="D58:I58"/>
+    <mergeCell ref="D59:I59"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="D61:I61"/>
+    <mergeCell ref="D62:I62"/>
+  </mergeCells>
   <hyperlinks>
     <hyperlink ref="D6" r:id="rId1" display="https://github.com/DevanshBajpai09/5-bugs-in-any-application-"/>
     <hyperlink ref="D11" r:id="rId2" display="https://github.com/DevanshBajpai09/Decision-tree"/>
@@ -3125,6 +3415,10 @@
     <hyperlink ref="D47" r:id="rId30" display="https://github.com/DevanshBajpai09/Selenium-Case-Study-6"/>
     <hyperlink ref="D56" r:id="rId31" display="https://github.com/DevanshBajpai09/Selenium-Java-Automation"/>
     <hyperlink ref="D58" r:id="rId32" display="https://github.com/DevanshBajpai09/POSTMAN---CaseStudy"/>
+    <hyperlink ref="D59" r:id="rId33" display="https://github.com/DevanshBajpai09/RestAssuredTesting"/>
+    <hyperlink ref="D60" r:id="rId34" display="https://github.com/DevanshBajpai09/BDDTestingPostRequestCaseStudy"/>
+    <hyperlink ref="D61" r:id="rId35" display="https://github.com/DevanshBajpai09/BDDTestingGetRequestCaseStudy"/>
+    <hyperlink ref="C1" r:id="rId36" display="https://github.com/DevanshBajpai09/ExcelSheetofTestingRepo"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
